--- a/Assets/ArtRes/Excel/成就表.xlsx
+++ b/Assets/ArtRes/Excel/成就表.xlsx
@@ -1961,7 +1961,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="12">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G6" s="12">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="12">
-        <v>590</v>
+        <v>300</v>
       </c>
       <c r="G7" s="12">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="12">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="G8" s="12">
         <v>0</v>
@@ -2039,7 +2039,7 @@
         <v>5</v>
       </c>
       <c r="F9" s="12">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="G9" s="12">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="12">
-        <v>2400</v>
+        <v>600</v>
       </c>
       <c r="G10" s="12">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>7</v>
       </c>
       <c r="F11" s="12">
-        <v>3700</v>
+        <v>700</v>
       </c>
       <c r="G11" s="12">
         <v>0</v>
@@ -2116,8 +2116,8 @@
       <c r="E12" s="13">
         <v>8</v>
       </c>
-      <c r="F12" s="13">
-        <v>4800</v>
+      <c r="F12" s="12">
+        <v>800</v>
       </c>
       <c r="G12" s="12">
         <v>0</v>
@@ -2143,7 +2143,7 @@
         <v>9</v>
       </c>
       <c r="F13" s="12">
-        <v>6500</v>
+        <v>900</v>
       </c>
       <c r="G13" s="12">
         <v>0</v>
@@ -2168,8 +2168,8 @@
       <c r="E14" s="13">
         <v>10</v>
       </c>
-      <c r="F14" s="13">
-        <v>8100</v>
+      <c r="F14" s="12">
+        <v>1000</v>
       </c>
       <c r="G14" s="12">
         <v>0</v>
@@ -2195,7 +2195,7 @@
         <v>11</v>
       </c>
       <c r="F15" s="13">
-        <v>9800</v>
+        <v>1500</v>
       </c>
       <c r="G15" s="12">
         <v>0</v>
@@ -2220,8 +2220,8 @@
       <c r="E16" s="13">
         <v>12</v>
       </c>
-      <c r="F16" s="13">
-        <v>12000</v>
+      <c r="F16" s="12">
+        <v>2000</v>
       </c>
       <c r="G16" s="12">
         <v>0</v>
@@ -2247,7 +2247,7 @@
         <v>13</v>
       </c>
       <c r="F17" s="13">
-        <v>15000</v>
+        <v>2500</v>
       </c>
       <c r="G17" s="12">
         <v>0</v>
@@ -2272,8 +2272,8 @@
       <c r="E18" s="13">
         <v>14</v>
       </c>
-      <c r="F18" s="13">
-        <v>18000</v>
+      <c r="F18" s="12">
+        <v>3000</v>
       </c>
       <c r="G18" s="12">
         <v>0</v>
@@ -2299,7 +2299,7 @@
         <v>15</v>
       </c>
       <c r="F19" s="13">
-        <v>22000</v>
+        <v>3500</v>
       </c>
       <c r="G19" s="12">
         <v>0</v>
@@ -2324,8 +2324,8 @@
       <c r="E20" s="13">
         <v>16</v>
       </c>
-      <c r="F20" s="13">
-        <v>27000</v>
+      <c r="F20" s="12">
+        <v>4000</v>
       </c>
       <c r="G20" s="12">
         <v>0</v>
@@ -2351,7 +2351,7 @@
         <v>17</v>
       </c>
       <c r="F21" s="13">
-        <v>33000</v>
+        <v>4500</v>
       </c>
       <c r="G21" s="12">
         <v>0</v>
@@ -2376,8 +2376,8 @@
       <c r="E22" s="13">
         <v>18</v>
       </c>
-      <c r="F22" s="13">
-        <v>39000</v>
+      <c r="F22" s="12">
+        <v>5000</v>
       </c>
       <c r="G22" s="12">
         <v>0</v>
@@ -2403,7 +2403,7 @@
         <v>19</v>
       </c>
       <c r="F23" s="13">
-        <v>47000</v>
+        <v>5500</v>
       </c>
       <c r="G23" s="12">
         <v>0</v>
@@ -2428,8 +2428,8 @@
       <c r="E24" s="13">
         <v>20</v>
       </c>
-      <c r="F24" s="13">
-        <v>55000</v>
+      <c r="F24" s="12">
+        <v>6000</v>
       </c>
       <c r="G24" s="12">
         <v>0</v>
@@ -2455,7 +2455,7 @@
         <v>21</v>
       </c>
       <c r="F25" s="13">
-        <v>65000</v>
+        <v>7000</v>
       </c>
       <c r="G25" s="12">
         <v>0</v>
@@ -2480,8 +2480,8 @@
       <c r="E26" s="13">
         <v>22</v>
       </c>
-      <c r="F26" s="13">
-        <v>75000</v>
+      <c r="F26" s="12">
+        <v>8000</v>
       </c>
       <c r="G26" s="12">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>23</v>
       </c>
       <c r="F27" s="13">
-        <v>87000</v>
+        <v>9000</v>
       </c>
       <c r="G27" s="12">
         <v>0</v>
@@ -2532,8 +2532,8 @@
       <c r="E28" s="13">
         <v>24</v>
       </c>
-      <c r="F28" s="13">
-        <v>100000</v>
+      <c r="F28" s="12">
+        <v>10000</v>
       </c>
       <c r="G28" s="12">
         <v>0</v>
@@ -2559,7 +2559,7 @@
         <v>25</v>
       </c>
       <c r="F29" s="13">
-        <v>123000</v>
+        <v>11000</v>
       </c>
       <c r="G29" s="12">
         <v>0</v>
@@ -2584,8 +2584,8 @@
       <c r="E30" s="13">
         <v>26</v>
       </c>
-      <c r="F30" s="13">
-        <v>150000</v>
+      <c r="F30" s="12">
+        <v>12000</v>
       </c>
       <c r="G30" s="12">
         <v>0</v>
@@ -2611,7 +2611,7 @@
         <v>27</v>
       </c>
       <c r="F31" s="13">
-        <v>180000</v>
+        <v>13000</v>
       </c>
       <c r="G31" s="12">
         <v>0</v>
@@ -2636,8 +2636,8 @@
       <c r="E32" s="13">
         <v>28</v>
       </c>
-      <c r="F32" s="13">
-        <v>234000</v>
+      <c r="F32" s="12">
+        <v>14000</v>
       </c>
       <c r="G32" s="12">
         <v>0</v>
@@ -2663,7 +2663,7 @@
         <v>29</v>
       </c>
       <c r="F33" s="13">
-        <v>300000</v>
+        <v>15000</v>
       </c>
       <c r="G33" s="12">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>30</v>
       </c>
       <c r="F34" s="13">
-        <v>375000</v>
+        <v>18000</v>
       </c>
       <c r="G34" s="12">
         <v>0</v>
@@ -2715,7 +2715,7 @@
         <v>31</v>
       </c>
       <c r="F35" s="13">
-        <v>456000</v>
+        <v>21000</v>
       </c>
       <c r="G35" s="12">
         <v>0</v>
@@ -2741,7 +2741,7 @@
         <v>32</v>
       </c>
       <c r="F36" s="13">
-        <v>500000</v>
+        <v>24000</v>
       </c>
       <c r="G36" s="12">
         <v>0</v>
@@ -2767,7 +2767,7 @@
         <v>33</v>
       </c>
       <c r="F37" s="13">
-        <v>555000</v>
+        <v>27000</v>
       </c>
       <c r="G37" s="12">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         <v>34</v>
       </c>
       <c r="F38" s="13">
-        <v>621000</v>
+        <v>30000</v>
       </c>
       <c r="G38" s="12">
         <v>0</v>
@@ -2819,7 +2819,7 @@
         <v>35</v>
       </c>
       <c r="F39" s="13">
-        <v>689000</v>
+        <v>33000</v>
       </c>
       <c r="G39" s="12">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         <v>36</v>
       </c>
       <c r="F40" s="13">
-        <v>743000</v>
+        <v>36000</v>
       </c>
       <c r="G40" s="12">
         <v>0</v>
@@ -2871,7 +2871,7 @@
         <v>37</v>
       </c>
       <c r="F41" s="13">
-        <v>875000</v>
+        <v>39000</v>
       </c>
       <c r="G41" s="12">
         <v>0</v>
@@ -2897,7 +2897,7 @@
         <v>38</v>
       </c>
       <c r="F42" s="13">
-        <v>923000</v>
+        <v>42000</v>
       </c>
       <c r="G42" s="12">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>39</v>
       </c>
       <c r="F43" s="13">
-        <v>950000</v>
+        <v>45000</v>
       </c>
       <c r="G43" s="12">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>40</v>
       </c>
       <c r="F44" s="13">
-        <v>1000000</v>
+        <v>50000</v>
       </c>
       <c r="G44" s="12">
         <v>0</v>
@@ -2975,7 +2975,7 @@
         <v>41</v>
       </c>
       <c r="F45" s="13">
-        <v>1100000</v>
+        <v>60000</v>
       </c>
       <c r="G45" s="12">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>42</v>
       </c>
       <c r="F46" s="13">
-        <v>1200000</v>
+        <v>70000</v>
       </c>
       <c r="G46" s="12">
         <v>0</v>
@@ -3027,7 +3027,7 @@
         <v>43</v>
       </c>
       <c r="F47" s="13">
-        <v>1300000</v>
+        <v>80000</v>
       </c>
       <c r="G47" s="12">
         <v>0</v>
@@ -3053,7 +3053,7 @@
         <v>44</v>
       </c>
       <c r="F48" s="13">
-        <v>1400000</v>
+        <v>90000</v>
       </c>
       <c r="G48" s="12">
         <v>0</v>
@@ -3079,7 +3079,7 @@
         <v>45</v>
       </c>
       <c r="F49" s="13">
-        <v>1500000</v>
+        <v>100000</v>
       </c>
       <c r="G49" s="12">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>46</v>
       </c>
       <c r="F50" s="13">
-        <v>1600000</v>
+        <v>200000</v>
       </c>
       <c r="G50" s="12">
         <v>0</v>
@@ -3131,7 +3131,7 @@
         <v>47</v>
       </c>
       <c r="F51" s="13">
-        <v>1800000</v>
+        <v>300000</v>
       </c>
       <c r="G51" s="12">
         <v>0</v>
@@ -3157,7 +3157,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="13">
-        <v>2000000</v>
+        <v>400000</v>
       </c>
       <c r="G52" s="12">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>49</v>
       </c>
       <c r="F53" s="13">
-        <v>2500000</v>
+        <v>500000</v>
       </c>
       <c r="G53" s="12">
         <v>0</v>
@@ -3209,7 +3209,7 @@
         <v>50</v>
       </c>
       <c r="F54" s="13">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="G54" s="12">
         <v>0</v>
@@ -3235,7 +3235,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="12">
-        <v>300</v>
+        <v>75</v>
       </c>
       <c r="G55" s="12">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="12">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="G56" s="12">
         <v>0</v>
@@ -3287,7 +3287,7 @@
         <v>3</v>
       </c>
       <c r="F57" s="12">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="G57" s="12">
         <v>0</v>
@@ -3313,7 +3313,7 @@
         <v>4</v>
       </c>
       <c r="F58" s="12">
-        <v>2000</v>
+        <v>450</v>
       </c>
       <c r="G58" s="12">
         <v>0</v>
@@ -3339,7 +3339,7 @@
         <v>5</v>
       </c>
       <c r="F59" s="12">
-        <v>3000</v>
+        <v>700</v>
       </c>
       <c r="G59" s="12">
         <v>0</v>
@@ -3365,7 +3365,7 @@
         <v>6</v>
       </c>
       <c r="F60" s="12">
-        <v>4000</v>
+        <v>900</v>
       </c>
       <c r="G60" s="12">
         <v>0</v>
@@ -3391,7 +3391,7 @@
         <v>7</v>
       </c>
       <c r="F61" s="12">
-        <v>9000</v>
+        <v>1800</v>
       </c>
       <c r="G61" s="12">
         <v>0</v>
@@ -3417,7 +3417,7 @@
         <v>8</v>
       </c>
       <c r="F62" s="13">
-        <v>12000</v>
+        <v>2700</v>
       </c>
       <c r="G62" s="12">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>9</v>
       </c>
       <c r="F63" s="12">
-        <v>15000</v>
+        <v>7200</v>
       </c>
       <c r="G63" s="12">
         <v>0</v>
@@ -3469,7 +3469,7 @@
         <v>10</v>
       </c>
       <c r="F64" s="13">
-        <v>20000</v>
+        <v>7000</v>
       </c>
       <c r="G64" s="12">
         <v>0</v>
@@ -3495,7 +3495,7 @@
         <v>11</v>
       </c>
       <c r="F65" s="13">
-        <v>30000</v>
+        <v>10500</v>
       </c>
       <c r="G65" s="12">
         <v>0</v>
@@ -3521,7 +3521,7 @@
         <v>12</v>
       </c>
       <c r="F66" s="13">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="G66" s="12">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>13</v>
       </c>
       <c r="F67" s="13">
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="G67" s="12">
         <v>0</v>
@@ -3573,7 +3573,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="13">
-        <v>80000</v>
+        <v>40000</v>
       </c>
       <c r="G68" s="12">
         <v>0</v>
@@ -3599,7 +3599,7 @@
         <v>15</v>
       </c>
       <c r="F69" s="13">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G69" s="12">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>16</v>
       </c>
       <c r="F70" s="13">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="G70" s="12">
         <v>0</v>
@@ -3651,7 +3651,7 @@
         <v>17</v>
       </c>
       <c r="F71" s="13">
-        <v>250000</v>
+        <v>120000</v>
       </c>
       <c r="G71" s="12">
         <v>0</v>
@@ -3677,7 +3677,7 @@
         <v>18</v>
       </c>
       <c r="F72" s="13">
-        <v>300000</v>
+        <v>150000</v>
       </c>
       <c r="G72" s="12">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>19</v>
       </c>
       <c r="F73" s="13">
-        <v>600000</v>
+        <v>300000</v>
       </c>
       <c r="G73" s="12">
         <v>0</v>
@@ -3729,7 +3729,7 @@
         <v>20</v>
       </c>
       <c r="F74" s="13">
-        <v>800000</v>
+        <v>400000</v>
       </c>
       <c r="G74" s="12">
         <v>0</v>
@@ -3755,7 +3755,7 @@
         <v>21</v>
       </c>
       <c r="F75" s="13">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="G75" s="12">
         <v>0</v>
@@ -3781,7 +3781,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="13">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G76" s="12">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>2</v>
       </c>
       <c r="F77" s="12">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G77" s="12">
         <v>0</v>
@@ -3833,7 +3833,7 @@
         <v>1</v>
       </c>
       <c r="F78" s="12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G78" s="12">
         <v>0</v>
@@ -3859,7 +3859,7 @@
         <v>2</v>
       </c>
       <c r="F79" s="12">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="G79" s="12">
         <v>0</v>
@@ -3885,7 +3885,7 @@
         <v>3</v>
       </c>
       <c r="F80" s="12">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G80" s="12">
         <v>0</v>
@@ -3911,7 +3911,7 @@
         <v>4</v>
       </c>
       <c r="F81" s="12">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="G81" s="12">
         <v>0</v>
@@ -3937,7 +3937,7 @@
         <v>5</v>
       </c>
       <c r="F82" s="12">
-        <v>25000</v>
+        <v>6000</v>
       </c>
       <c r="G82" s="12">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>6</v>
       </c>
       <c r="F83" s="12">
-        <v>60000</v>
+        <v>8000</v>
       </c>
       <c r="G83" s="12">
         <v>0</v>
@@ -3989,7 +3989,7 @@
         <v>7</v>
       </c>
       <c r="F84" s="12">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G84" s="12">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>8</v>
       </c>
       <c r="F85" s="13">
-        <v>150000</v>
+        <v>12000</v>
       </c>
       <c r="G85" s="12">
         <v>0</v>
@@ -4041,7 +4041,7 @@
         <v>9</v>
       </c>
       <c r="F86" s="12">
-        <v>200000</v>
+        <v>30000</v>
       </c>
       <c r="G86" s="12">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="13">
-        <v>300000</v>
+        <v>40000</v>
       </c>
       <c r="G87" s="12">
         <v>0</v>
@@ -4093,7 +4093,7 @@
         <v>11</v>
       </c>
       <c r="F88" s="12">
-        <v>400000</v>
+        <v>60000</v>
       </c>
       <c r="G88" s="12">
         <v>0</v>
@@ -4119,7 +4119,7 @@
         <v>12</v>
       </c>
       <c r="F89" s="12">
-        <v>600000</v>
+        <v>80000</v>
       </c>
       <c r="G89" s="12">
         <v>0</v>
@@ -4145,7 +4145,7 @@
         <v>13</v>
       </c>
       <c r="F90" s="12">
-        <v>800000</v>
+        <v>100000</v>
       </c>
       <c r="G90" s="12">
         <v>0</v>
@@ -4171,7 +4171,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="12">
-        <v>1000000</v>
+        <v>120000</v>
       </c>
       <c r="G91" s="12">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>15</v>
       </c>
       <c r="F92" s="12">
-        <v>2000000</v>
+        <v>160000</v>
       </c>
       <c r="G92" s="12">
         <v>0</v>
@@ -4223,7 +4223,7 @@
         <v>16</v>
       </c>
       <c r="F93" s="13">
-        <v>3000000</v>
+        <v>200000</v>
       </c>
       <c r="G93" s="12">
         <v>0</v>
@@ -4249,7 +4249,7 @@
         <v>17</v>
       </c>
       <c r="F94" s="12">
-        <v>4000000</v>
+        <v>400000</v>
       </c>
       <c r="G94" s="12">
         <v>0</v>
@@ -4275,7 +4275,7 @@
         <v>18</v>
       </c>
       <c r="F95" s="13">
-        <v>6000000</v>
+        <v>600000</v>
       </c>
       <c r="G95" s="12">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>19</v>
       </c>
       <c r="F96" s="12">
-        <v>8000000</v>
+        <v>1000000</v>
       </c>
       <c r="G96" s="12">
         <v>0</v>
@@ -4353,7 +4353,7 @@
         <v>1</v>
       </c>
       <c r="F98" s="13">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="G98" s="12">
         <v>0</v>
@@ -4379,7 +4379,7 @@
         <v>2</v>
       </c>
       <c r="F99" s="12">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="G99" s="12">
         <v>0</v>
@@ -4405,7 +4405,7 @@
         <v>3</v>
       </c>
       <c r="F100" s="12">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="G100" s="12">
         <v>0</v>
@@ -4431,7 +4431,7 @@
         <v>4</v>
       </c>
       <c r="F101" s="12">
-        <v>50000</v>
+        <v>5000</v>
       </c>
       <c r="G101" s="12">
         <v>0</v>
@@ -4457,7 +4457,7 @@
         <v>5</v>
       </c>
       <c r="F102" s="12">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G102" s="12">
         <v>0</v>
@@ -4483,7 +4483,7 @@
         <v>6</v>
       </c>
       <c r="F103" s="13">
-        <v>200000</v>
+        <v>20000</v>
       </c>
       <c r="G103" s="12">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>7</v>
       </c>
       <c r="F104" s="12">
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="G104" s="12">
         <v>0</v>
@@ -4535,7 +4535,7 @@
         <v>8</v>
       </c>
       <c r="F105" s="13">
-        <v>500000</v>
+        <v>50000</v>
       </c>
       <c r="G105" s="12">
         <v>0</v>
@@ -4561,7 +4561,7 @@
         <v>9</v>
       </c>
       <c r="F106" s="12">
-        <v>750000</v>
+        <v>75000</v>
       </c>
       <c r="G106" s="12">
         <v>0</v>
@@ -4587,7 +4587,7 @@
         <v>10</v>
       </c>
       <c r="F107" s="13">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="G107" s="12">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         <v>5</v>
       </c>
       <c r="F112" s="12">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="G112" s="12">
         <v>0</v>
@@ -4769,7 +4769,7 @@
         <v>1</v>
       </c>
       <c r="F114" s="12">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="G114" s="12">
         <v>0</v>
@@ -4795,7 +4795,7 @@
         <v>2</v>
       </c>
       <c r="F115" s="12">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="G115" s="12">
         <v>0</v>
@@ -4847,7 +4847,7 @@
         <v>4</v>
       </c>
       <c r="F117" s="12">
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="G117" s="12">
         <v>0</v>
